--- a/assets/tosspay-coupon-search-ad-prd.xlsx
+++ b/assets/tosspay-coupon-search-ad-prd.xlsx
@@ -706,7 +706,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D6" s="24" t="n"/>
@@ -770,7 +770,7 @@
       <c r="F14" s="24" t="n"/>
       <c r="G14" s="24" t="n"/>
     </row>
-    <row r="15" ht="59.40000000000001" customHeight="1">
+    <row r="15" ht="118.8" customHeight="1">
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>사용자 문제</t>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>사용자는 쿠폰과 제휴처가 많아질수록 원하는 혜택을 탐색하기 어렵고, 광고주는 큐레이션 슬롯이나 고정형 최상단 광고만으로는 검색 의도가 높은 사용자에게 효율적으로 도달하기 어렵다. 토스 내부에서도 검색광고가 실제 추가 결제를 만드는지, 기존 오가닉 쿠폰과 디스플레이 광고를 잠식하는지 불확실하다.</t>
+          <t>사용자는 쿠폰과 제휴처가 많아질수록 원하는 혜택을 탐색하기 어렵고, 광고주는 큐레이션 슬롯이나 고정형 최상단 광고만으로는 검색 의도가 높은 사용자에게 효율적으로 도달하기 어렵다. 쿠폰·성과형 광고는 구매 직전에 노출될 수 있어 원래 전환할 고객에게도 할인이 제공되고 해당 전환이 광고 성과로 집계될 수 있다. 이에 광고주는 광고가 늘린 매출인지 원래 구매할 고객의 전환인지 구분하기 어려워 광고비 누수를 우려한다. ANA 조사에서 리테일 미디어 광고주의 71%가 증분성을 최우선 핵심 지표로 꼽았다는 공개 결과가 있으나, 조사 범위와 수치의 최신 원문은 출시 전 재검증해야 한다. 따라서 본 검색광고는 자연 전환과 광고 전환을 구분하는 측정 체계를 갖춰야 하며, 토스 내부에서도 검색광고가 실제 추가 결제를 만드는지와 기존 오가닉 쿠폰·디스플레이 광고를 잠식하는지를 검증해야 한다.</t>
         </is>
       </c>
       <c r="D15" s="24" t="n"/>
@@ -1384,7 +1384,10 @@
 3. ○ Given 결제가 취소 또는 환불되었을 때, When 후속 이벤트가 반영되면, Then 전환 수·거래액·ROAS·정산 금액이 정책에 따라 갱신된다.
 4. ○ Given 사용자 홀드아웃 그룹이 설정되었을 때, When 실험 기간이 종료되면, Then 노출군과 대조군의 검색·쿠폰 발급·토스페이 결제 차이와 신뢰구간을 제공한다.
 5. ○ Given 광고주가 대시보드에 접근할 때, When 권한을 검증하면, Then 본인 캠페인 데이터만 조회되고 원시 개인정보는 노출되지 않는다.
-6. ○ 리포트 신선도는 파일럿 가정상 일반 지표 1시간 이내, 결제·정산 확정 지표 24시간 이내로 제공하며 실제 SLA는 기술 검증 후 확정한다.</t>
+6. ○ 리포트 신선도는 파일럿 가정상 일반 지표 1시간 이내, 결제·정산 확정 지표 24시간 이내로 제공하며 실제 SLA는 기술 검증 후 확정한다.
+7. ○ Given 광고 클릭과 연결된 쿠폰 발급 또는 토스페이 결제가 발생했을 때, When 전환 리포트를 집계하면, Then 신규 고객과 기존 고객의 발급·결제 성과를 구분해 제공한다.
+8. ○ Given 사용자 홀드아웃 대조군과 광고 노출군의 측정 기간이 종료되었을 때, When 증분 효과를 산출하면, Then 대조군 대비 더 발생한 쿠폰 발급·토스페이 결제만 순증 성과로 집계한다.
+9. ○ Given 재유입 또는 중복 결제 이벤트가 발생했을 때, When 증분 효과를 산출하면, Then 멱등키와 전환 여정 기준으로 보정한 중복·재유입 전환은 순증 성과에서 제외한다.</t>
         </is>
       </c>
       <c r="F39" s="10" t="inlineStr">
@@ -1477,6 +1480,7 @@
 • 표시: - 운영 리포트는 노출군·대조군의 차이와 신뢰구간을 집계 수준으로 표시한다.
 • 권한 &amp; 접근: - 데이터 분석가와 권한을 가진 토스 운영자만 실험 분석 결과를 조회할 수 있다.
 • 비즈니스 규칙: - 홀드아웃 A/B의 증분성은 확대·축소 의사결정 지표이며 CPC 또는 CPS 과금 기준이 아니다.
+• 증분성 측정 결과는 광고 매출 또는 유효 CPC·CPS 과금액을 차감하는 기준으로 사용하지 않는다.
 • 데이터: - 전환 여정은 클릭 ID, 쿠폰 ID, 전환 ID, 캠페인, 실험군, 결제 상태, 환불 상태, 이벤트 시각을 가진다.</t>
         </is>
       </c>

--- a/assets/tosspay-coupon-search-ad-prd.xlsx
+++ b/assets/tosspay-coupon-search-ad-prd.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>토스페이 쿠폰 광고주와 파트너가 증가하면 쿠폰 종류가 늘어나고, 제한된 큐레이션 슬롯만으로는 사용자가 원하는 쿠폰을 찾기 어려워질 수 있다. 이에 따라 사용자의 검색 행동을 활용한 수요 포착형 광고 지면이 필요하다. 본 상품은 신규 또는 기존 토스 쿠폰 검색 결과 지면에 광고 수익화 레이어를 추가하는 것으로, 현재 검색 기능의 유무·범위·동작은 내부 확인을 전제로 한다. 검색 기능이 이미 있다면 본 상품은 그 위에 신설하는 광고 상품이다. 기존 오늘딜·브랜드관 등 큐레이션은 수요를 발견하게 하는 퍼널 상단 상품이고, 최상단 AD는 검색과 무관한 CPT 고정 상품인 반면, 검색 성과형 광고는 사용자의 검색 의도에 반응하는 퍼널 하단 상품이다. 공개 자료에서 아마존 리테일 미디어 광고 규모가 연간 약 600억 달러, 광고수익 증가율이 약 17.7%로 보고되었고, 아마존의 상품 검색 광고인 스폰서 상품은 검색 결과 CPC 모델의 대표 사례로 제시된다. 네이버 커머스 광고 비중은 2019년 약 18.2%에서 2025년 약 30.6%로 증가했다는 공개 자료가 있다. 또한 공개된 소비자 실험에서는 구매의 약 51.7%가 상위 5개 상품에 집중되고 필터 미사용률이 약 83.8%로 보고되었으며, 검색 상단 노출이 가격 프리미엄에도 구매 가능성을 높인다는 결과가 제시되었다. 소비쿠폰 관련 공개 보도에서는 4주 소진율 약 75%, 8주 소진율 약 90%가 언급되었고, 배달·커머스 영역에서 할인 혜택이 선택 요인으로 작동한다는 사례가 있다. 네이버 쇼핑검색, 쿠팡, 아마존의 공개 광고 사례에서는 검색광고의 높은 효율과 롱테일 광고주의 성과가 제시된다. 다만 위 수치는 출처별 조사 방법과 정의가 다르며 토스의 성과를 의미하지 않는다. 수치와 출처는 출시 전 원문 및 최신 자료를 재검증해야 한다. 토스는 결제 및 마이데이터 기반의 1st-party 행동 신호와 쿠폰 사용 결과를 활용해 검색어·사용자 의도·예상 전환율을 연결할 가능성이 있으며, 쿠폰 사용을 토스페이 결제로 연결함으로써 광고가 결제를 유도하는 레버가 될 수 있다. 토스 광고주가 약 2배 증가하고 누적 파트너가 약 1만 곳이라는 내부 또는 공개 커뮤니케이션 수치는 별도 검증이 필요하며, 본 제품의 시장 진입 판단에는 내부 데이터 확인을 전제로 한다.</t>
+          <t>토스페이 쿠폰 광고주와 파트너가 증가하면 쿠폰 종류가 늘어나고, 제한된 큐레이션 슬롯만으로는 사용자가 원하는 쿠폰을 찾기 어려워질 수 있다. 이에 따라 사용자의 검색 행동을 활용한 수요 포착형 광고 지면이 필요하다. 본 상품은 이미 제휴 쿠폰으로 구성된 신규 또는 기존 토스 쿠폰 검색 결과에 상단 노출 입찰 경매(eCPM)와 입찰 상단을 신설하는 광고 수익화 레이어다. 현재 검색 기능의 유무·범위·동작은 내부 확인을 전제로 하며 검색 기능이 이미 있다면 그 위에 광고 상품을 신설한다. 기존 오늘딜·브랜드관 등 큐레이션은 수요를 발견하게 하는 퍼널 상단 상품이고, 최상단 AD는 검색과 무관한 CPT 고정 상품인 반면, 검색 성과형 광고는 사용자의 검색 의도에 반응하는 퍼널 하단 상품이다. 공개 자료에서 아마존 리테일 미디어 광고 규모가 연간 약 600억 달러, 광고수익 증가율이 약 17.7%로 보고되었고, 아마존의 상품 검색 광고인 스폰서 상품은 검색 결과 CPC 모델의 대표 사례로 제시된다. 네이버 커머스 광고 비중은 2019년 약 18.2%에서 2025년 약 30.6%로 증가했다는 공개 자료가 있다. 또한 공개된 소비자 실험에서는 구매의 약 51.7%가 상위 5개 상품에 집중되고 필터 미사용률이 약 83.8%로 보고되었으며, 검색 상단 노출이 가격 프리미엄에도 구매 가능성을 높인다는 결과가 제시되었다. 소비쿠폰 관련 공개 보도에서는 4주 소진율 약 75%, 8주 소진율 약 90%가 언급되었고, 배달·커머스 영역에서 할인 혜택이 선택 요인으로 작동한다는 사례가 있다. 네이버 쇼핑검색, 쿠팡, 아마존의 공개 광고 사례에서는 검색광고의 높은 효율과 롱테일 광고주의 성과가 제시된다. 다만 위 수치는 출처별 조사 방법과 정의가 다르며 토스의 성과를 의미하지 않는다. 수치와 출처는 출시 전 원문 및 최신 자료를 재검증해야 한다. 토스는 결제 및 마이데이터 기반의 1st-party 행동 신호와 쿠폰 사용 결과를 활용해 검색어·사용자 의도·예상 전환율을 연결할 가능성이 있으며, 쿠폰 사용을 토스페이 결제로 연결함으로써 광고가 결제를 유도하는 레버가 될 수 있다. 토스 광고주가 약 2배 증가하고 누적 파트너가 약 1만 곳이라는 내부 또는 공개 커뮤니케이션 수치는 별도 검증이 필요하며, 본 제품의 시장 진입 판단에는 내부 데이터 확인을 전제로 한다.</t>
         </is>
       </c>
       <c r="D14" s="24" t="n"/>
@@ -770,7 +770,7 @@
       <c r="F14" s="24" t="n"/>
       <c r="G14" s="24" t="n"/>
     </row>
-    <row r="15" ht="118.8" customHeight="1">
+    <row r="15" ht="158.4" customHeight="1">
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>사용자 문제</t>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>사용자는 쿠폰과 제휴처가 많아질수록 원하는 혜택을 탐색하기 어렵고, 광고주는 큐레이션 슬롯이나 고정형 최상단 광고만으로는 검색 의도가 높은 사용자에게 효율적으로 도달하기 어렵다. 쿠폰·성과형 광고는 구매 직전에 노출될 수 있어 원래 전환할 고객에게도 할인이 제공되고 해당 전환이 광고 성과로 집계될 수 있다. 이에 광고주는 광고가 늘린 매출인지 원래 구매할 고객의 전환인지 구분하기 어려워 광고비 누수를 우려한다. ANA 조사에서 리테일 미디어 광고주의 71%가 증분성을 최우선 핵심 지표로 꼽았다는 공개 결과가 있으나, 조사 범위와 수치의 최신 원문은 출시 전 재검증해야 한다. 따라서 본 검색광고는 자연 전환과 광고 전환을 구분하는 측정 체계를 갖춰야 하며, 토스 내부에서도 검색광고가 실제 추가 결제를 만드는지와 기존 오가닉 쿠폰·디스플레이 광고를 잠식하는지를 검증해야 한다.</t>
+          <t>사용자는 쿠폰과 제휴처가 많아질수록 원하는 혜택을 탐색하기 어렵고, 광고주는 큐레이션 슬롯이나 고정형 최상단 광고만으로는 검색 의도가 높은 사용자에게 효율적으로 도달하기 어렵다. 토스페이 쿠폰은 토스 앱에서 미리 받아두고 토스페이 결제 시 자동 적용되는 형태가 많다. 따라서 원래 구매할 고객이 이왕이면 토스페이 쿠폰을 받고 결제하는 경우, 쿠폰이 없어도 발생했을 전환이 광고 성과로 집계될 수 있다. 예를 들어 무신사에서 옷을 살 사용자가 쿠폰이 없어도 결제했을 상황에서 토스페이 쿠폰을 알고 받아 결제할 수 있다. 이에 광고주는 실제 광고 쿠폰을 보고 전환한 고객인지, 원래 전환할 고객이 쿠폰만 받은 것인지를 구분하지 못해 광고비 누수를 우려한다. ANA 조사에서 리테일 미디어 광고주의 71%가 증분성을 최우선 핵심 지표로 꼽았다는 공개 결과가 있으나, 조사 범위와 수치의 최신 원문은 출시 전 재검증해야 한다. 따라서 본 검색광고는 자연 전환과 광고 전환을 구분하는 측정 체계를 갖춰야 하며, 토스 내부에서도 검색광고가 실제 추가 결제를 만드는지와 기존 일반 노출 쿠폰·디스플레이 광고를 잠식하는지를 검증해야 한다.</t>
         </is>
       </c>
       <c r="D15" s="24" t="n"/>
@@ -794,7 +794,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>사용자의 검색어와 카테고리를 기준으로 관련 쿠폰 광고 후보를 구성하고, CPC 입찰가·예상 전환율 품질점수·검색 적합도를 결합한 eCPM 방식으로 순위를 결정한다. 광고는 검색 결과 최상단 및 오가닉 결과와 혼합된 위치에 노출하되, 관련성 최소 기준, 신규 광고주 탐색 노출, 광고주별 상단 점유 제한, 예산 페이싱, 롱테일 키워드 분산을 적용한다. 토스 기존 쿠폰 광고의 보장형 전환당 과금과 달리 검색광고의 기본 과금은 CPC로 하며, 검색이 사용자의 직접 의도를 반영한 고의도 트래픽이고 네이버 쇼핑검색·쿠팡·아마존의 커머스 검색광고가 CPC 경매를 표준으로 사용한다는 점을 파일럿 가정으로 둔다. 보장형을 선호하는 광고주에게는 검증된 범위에서 CPS 전환당 과금 또는 보장형 티어를 선택 옵션으로 제공한다. 쿠폰 할인액의 부담 주체와 CPC 광고비는 별개로 관리하며, 할인 부담 구조는 기존 토스페이 쿠폰 정책을 따르되 정확한 분담 기준은 내부 정책 확인 후 확정한다. 본 상품은 신규 또는 기존 쿠폰 검색 결과 지면에 검색광고 수익화 레이어를 추가하는 것으로, 현재 토스 쿠폰 검색 기능의 유무·범위·동작은 내부 확인을 전제로 하며 검색 기능이 이미 있다면 그 위에 광고 상품을 신설한다.</t>
+          <t>사용자의 검색어와 카테고리를 기준으로 관련 쿠폰 광고 후보를 구성하고, CPC 입찰가·예상 전환율 품질점수·검색 적합도를 결합한 eCPM 방식으로 순위를 결정한다. 이미 제휴 쿠폰으로 구성된 검색 결과에 입찰 상단 노출 경매를 신설하고, 입찰 상단과 일반 노출(입찰 미참여 제휴 쿠폰)을 혼합해 배치한다. 관련성 최소 기준, 신규 광고주 탐색 노출, 광고주별 상단 점유 제한, 예산 페이싱, 롱테일 키워드 분산을 적용한다. 토스 기존 쿠폰 광고의 보장형 전환당 과금과 달리 검색광고의 기본 과금은 CPC로 하며, 검색이 사용자의 직접 의도를 반영한 고의도 트래픽이고 네이버 쇼핑검색·쿠팡·아마존의 커머스 검색광고가 CPC 경매를 표준으로 사용한다는 점을 파일럿 가정으로 둔다. 보장형을 선호하는 광고주에게는 검증된 범위에서 CPS 전환당 과금 또는 보장형 티어를 선택 옵션으로 제공한다. 쿠폰 할인액의 부담 주체와 CPC 광고비는 별개로 관리하며, 할인 부담 구조는 기존 토스페이 쿠폰 정책을 따르되 정확한 분담 기준은 내부 정책 확인 후 확정한다. 본 상품은 신규 또는 기존 토스 쿠폰 검색 결과 지면에 검색광고 수익화 레이어를 추가하는 것으로, 현재 토스 쿠폰 검색 기능의 유무·범위·동작은 내부 확인을 전제로 하며 검색 기능이 이미 있다면 그 위에 광고 상품을 신설한다.</t>
         </is>
       </c>
       <c r="D16" s="24" t="n"/>
@@ -802,7 +802,7 @@
       <c r="F16" s="24" t="n"/>
       <c r="G16" s="24" t="n"/>
     </row>
-    <row r="17" ht="118.8" customHeight="1">
+    <row r="17" ht="138.6" customHeight="1">
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>차별점</t>
@@ -810,7 +810,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>최상단 AD는 검색어와 무관하게 고정된 한정 슬롯을 CPT로 판매하는 상품이고, 본 상품은 사용자의 검색 의도에 반응해 경쟁 노출되는 CPC 검색광고 상품이다. 기존 보장형 CPS 큐레이션·오늘딜은 수요를 발견시키는 퍼널 상단 상품이고, 검색 CPC는 이미 형성된 수요를 포착하는 퍼널 하단 상품이므로 서로 대체하지 않고 병행·보완한다. 보장형을 선호하는 광고주에게는 CPS 전환당·보장형 티어를 선택 옵션으로 제공한다. 토스는 결제·쿠폰 사용 결과와 마이데이터 기반의 1st-party 신호를 활용해 예상 전환율과 적합도를 개선할 가능성이 있으며, 쿠폰 사용을 토스페이 결제와 직접 연결해 광고 성과를 결제 활성화까지 측정할 수 있다. 다만 데이터 활용은 개인정보 보호, 동의, 목적 제한, 비식별·집계 처리 정책을 준수해야 하며, 실제 우위는 파일럿 A/B로 입증한다.</t>
+          <t>최상단 AD는 검색어와 무관하게 고정된 한정 슬롯을 CPT로 판매하는 상품이고, 본 상품은 이미 제휴 쿠폰으로 구성된 검색 결과에 상단 노출 입찰 경매(eCPM)를 신설해 사용자의 검색 의도에 반응하는 CPC 검색광고 상품이다. 기존 보장형 CPS 큐레이션·오늘딜은 수요를 발견시키는 퍼널 상단 상품이고, 검색 CPC는 이미 형성된 수요를 포착하는 퍼널 하단 상품이므로 서로 대체하지 않고 병행·보완한다. 보장형을 선호하는 광고주에게는 CPS 전환당·보장형 티어를 선택 옵션으로 제공한다. 토스는 결제·쿠폰 사용 결과와 마이데이터 기반의 1st-party 신호를 활용해 예상 전환율과 적합도를 개선할 가능성이 있으며, 쿠폰 사용을 토스페이 결제와 직접 연결해 광고 성과를 결제 활성화까지 측정할 수 있다. 다만 데이터 활용은 개인정보 보호, 동의, 목적 제한, 비식별·집계 처리 정책을 준수해야 하며, 실제 우위는 파일럿 A/B로 입증한다.</t>
         </is>
       </c>
       <c r="D17" s="24" t="n"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>사용자가 토스 혜택·쿠폰 화면에서 ‘운동화 할인’ 또는 특정 브랜드를 검색하면 시스템은 검색어를 정규화하고 관련 카테고리를 판정한다. 경매 시스템은 자격을 갖춘 광고주의 키워드·카테고리 캠페인을 조회하고, 입찰가·예상 전환율·검색 적합도·가드레일을 반영해 광고 후보를 선정한다. 사용자는 광고 표지가 포함된 쿠폰을 최상단 또는 오가닉 결과와 혼합된 위치에서 확인하고 쿠폰 상세로 이동한다. 쿠폰을 발급한 뒤 토스페이로 결제하면 클릭과 쿠폰 발급, 결제 확정이 하나의 전환 여정으로 기록된다. 광고주는 대시보드에서 노출·클릭·쿠폰 발급·토스페이 결제·비용·ROAS를 확인한다. 파일럿에서는 광고 노출이 없는 사용자 홀드아웃 그룹과 비교해 광고가 없었어도 발생했을 검색·쿠폰 발급·결제를 제외한 순증 효과를 측정한다. 사용자 홀드아웃 A/B는 순증 효과 검증과 확대 여부 판단을 위한 실험이며 광고 과금 기준이 아니고, 과금은 유효 CPC 클릭 기준으로 처리한다.</t>
+          <t>사용자가 토스 혜택·쿠폰 화면에서 ‘운동화 할인’ 또는 특정 브랜드를 검색하면 시스템은 검색어를 정규화하고 관련 카테고리를 판정한다. 경매 시스템은 자격을 갖춘 광고주의 키워드·카테고리 캠페인을 조회하고, 입찰가·예상 전환율·검색 적합도·가드레일을 반영해 입찰 상단 후보를 선정한다. 사용자는 광고 표지가 포함된 쿠폰을 최상단 또는 일반 노출 결과와 혼합된 위치에서 확인하고 쿠폰 상세로 이동한다. 쿠폰을 발급한 뒤 토스페이로 결제하면 클릭과 쿠폰 발급, 결제 확정이 하나의 전환 여정으로 기록된다. 광고주는 대시보드에서 노출·클릭·쿠폰 발급·토스페이 결제·비용·ROAS를 확인한다. 파일럿에서는 광고 노출이 없는 사용자 홀드아웃 그룹과 비교해 광고가 없었어도 발생했을 검색·쿠폰 발급·결제를 제외한 순증 효과를 측정한다. 사용자 홀드아웃 A/B는 순증 효과 검증과 확대 여부 판단을 위한 실험이며 광고 과금 기준이 아니고, 과금은 유효 CPC 클릭 기준으로 처리한다.</t>
         </is>
       </c>
       <c r="D19" s="24" t="n"/>
@@ -850,7 +850,7 @@
       <c r="F19" s="24" t="n"/>
       <c r="G19" s="24" t="n"/>
     </row>
-    <row r="20" ht="217.8" customHeight="1">
+    <row r="20" ht="237.6" customHeight="1">
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>핵심 지표</t>
@@ -858,7 +858,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>모든 목표·기준값은 파일럿 가정이다. 성장 지표: 검색광고 매출, 집행 광고주 수, 쿠폰광고 미경험 신규 광고주의 캠페인 전환 수를 측정한다. 토스페이 지표: 검색 경유 쿠폰 발급 수·사용 수, 토스페이 결제 건수·거래액, 검색 클릭 대비 결제 전환율을 측정한다. 광고 건전성 지표: 검색 CTR, 쿠폰 발급 CVR, 토스페이 결제 CVR, 평균 CPC, 광고주 ROAS, 무효 클릭률, 광고 밀도, 오가닉 쿠폰 잠식률, 디스플레이 매출 유지율을 측정한다. 파일럿 목표 가정은 다음과 같다: 검색 경유 쿠폰의 클릭 대비 토스페이 결제 전환율은 대조군 대비 상대적 순증 효과 확인, 집행 광고주 중 신규 광고주 비중은 30% 이상, 캠페인 유지 광고주 비중은 50% 이상, 무효 클릭률은 2% 이하, 오가닉 쿠폰 잠식률은 10% 이하, 기존 디스플레이 매출 유지율은 90% 이상, 한 검색 결과 내 광고 비중은 30% 이하로 설정한다. 확대 게이트는 통계적으로 유의한 순증 결제 효과, 광고주 재집행, 허용 가능한 잠식률·무효 클릭률·사용자 불만 수준을 동시에 충족하는 경우로 한다. 축소 또는 중단 기준은 검색광고 노출군의 토스페이 결제가 대조군보다 증가하지 않거나, 오가닉 잠식률이 15%를 초과하거나, 무효 클릭률이 5%를 초과하거나, 광고 밀도·신고율이 사전 임계값을 초과하는 경우로 가정한다. 사용자 홀드아웃 A/B는 광고가 없어도 발생했을 전환을 제외한 순증 효과와 확대 여부를 검증하는 의사결정 지표이며, CPC 클릭 과금 또는 CPS 과금의 기준으로 사용하지 않는다. 정확한 표본 수, 유의수준, 최소 검출 효과는 사전 검정력 분석으로 확정한다.</t>
+          <t>모든 목표·기준값은 파일럿 가정이다. 성장 지표: 검색광고 매출, 집행 광고주 수, 쿠폰광고 미경험 신규 광고주의 캠페인 전환 수를 측정한다. 토스페이 지표: 검색 경유 쿠폰 발급 수·사용 수, 토스페이 결제 건수·거래액, 검색 클릭 대비 결제 전환율을 측정한다. 광고 건전성 지표: 검색 CTR, 쿠폰 발급 CVR, 토스페이 결제 CVR, 평균 CPC, 광고주 ROAS, 무효 클릭률, 입찰 상단 비중, 일반 노출 쿠폰 잠식률, 디스플레이 매출 유지율을 측정한다. 파일럿 목표 가정은 다음과 같다: 검색 경유 쿠폰의 클릭 대비 토스페이 결제 전환율은 대조군 대비 상대적 순증 효과 확인, 집행 광고주 중 신규 광고주 비중은 30% 이상, 캠페인 유지 광고주 비중은 50% 이상, 무효 클릭률은 2% 이하, 일반 노출 쿠폰 잠식률은 10% 이하, 기존 디스플레이 매출 유지율은 90% 이상, 한 검색 결과 내 입찰 상단 비중은 30% 이하로 설정한다. 확대 게이트는 통계적으로 유의한 순증 결제 효과, 광고주 재집행, 허용 가능한 잠식률·무효 클릭률·사용자 불만 수준을 동시에 충족하는 경우로 한다. 축소 또는 중단 기준은 검색광고 노출군의 토스페이 결제가 대조군보다 증가하지 않거나, 일반 노출 쿠폰 잠식률이 15%를 초과하거나, 무효 클릭률이 5%를 초과하거나, 입찰 상단 비중·신고율이 사전 임계값을 초과하는 경우로 가정한다. 사용자 홀드아웃 A/B는 광고가 없어도 발생했을 전환을 제외한 순증 효과와 확대 여부를 검증하는 의사결정 지표이며, CPC 클릭 과금 또는 CPS 과금의 기준으로 사용하지 않는다. 정확한 표본 수, 유의수준, 최소 검출 효과는 사전 검정력 분석으로 확정한다.</t>
         </is>
       </c>
       <c r="D20" s="24" t="n"/>
@@ -874,7 +874,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>첫째, 쿠폰 검색량이 충분하지 않을 수 있다. 쇼핑·리테일과 뷰티·라이프스타일 카테고리에서 먼저 검증하고 사용자 홀드아웃 A/B로 순증 효과를 측정한다. 둘째, 검색광고가 기존 디스플레이 예산을 잠식할 수 있다. 통합 매출을 KPI로 관리하고 디스플레이 최소 노출 및 예산 이동 모니터링을 적용한다. 셋째, 검색이라도 클릭 낭비가 발생할 수 있다. 품질점수·검색 적합도·무효 클릭 탐지·예산 페이싱을 적용한다. 넷째, 전환율이 높은 대형 광고주가 상단을 독점할 수 있다. 관련성 최소 기준, 신규 광고주 콜드스타트 탐색 노출, 광고주별 다양성 캡, 롱테일 키워드 분산을 적용한다. 다섯째, 쿠폰 발급과 결제 사이의 어트리뷰션 오류가 발생할 수 있다. 클릭 ID와 전환 ID, 멱등키, 환불 이벤트를 활용해 중복·취소를 보정한다. 여섯째, 개인화·마이데이터 활용이 개인정보 침해로 오해될 수 있으므로 동의·목적 제한·역할기반 접근·집계 리포팅을 적용한다. 일곱째, CPS 보장형 상품은 부정 전환과 재무 리스크가 있으므로 초기에는 제한된 광고주와 한도 내에서 검증한다.</t>
+          <t>첫째, 쿠폰 검색량이 충분하지 않을 수 있다. 쇼핑·리테일과 뷰티·라이프스타일 카테고리에서 먼저 검증하고 사용자 홀드아웃 A/B로 순증 효과를 측정한다. 둘째, 기존 광고 구좌(디스플레이·CPT)와의 자가잠식으로 예산이 이전돼도 전체 매출의 순증이 없을 수 있다. 통합 매출을 핵심 지표로 관리하고 디스플레이 최소 노출 및 예산 이동 모니터링을 적용한다. 셋째, 검색이라도 클릭 낭비가 발생할 수 있다. 품질점수·검색 적합도·무효 클릭 탐지·예산 페이싱을 적용한다. 넷째, 대형 광고주의 최상단 구좌 단독점유가 발생할 수 있다. 관련성 최소 기준, 신규 광고주 콜드스타트 탐색 노출, 광고주별 다양성 캡, 롱테일 키워드 분산을 적용한다. 다섯째, 쿠폰 발급과 결제 사이의 어트리뷰션 오류가 발생할 수 있다. 클릭 ID와 전환 ID, 멱등키, 환불 이벤트를 활용해 중복·취소를 보정한다. 여섯째, 개인화·마이데이터 활용이 개인정보 침해로 오해될 수 있으므로 동의·목적 제한·역할기반 접근·집계 리포팅을 적용한다. 일곱째, CPS 보장형 상품은 부정 전환과 재무 리스크가 있으므로 초기에는 제한된 광고주와 한도 내에서 검증한다.</t>
         </is>
       </c>
       <c r="D21" s="24" t="n"/>
@@ -1156,19 +1156,19 @@
     <row r="34">
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>3 검색 노출·오가닉 혼합 및 독식 방지</t>
+          <t>3 입찰 상단·일반 노출 혼합 및 독식 방지</t>
         </is>
       </c>
       <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="n"/>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>광고는 검색 결과 최상단과 오가닉 결과 사이의 혼합 영역에 배치하고 광고 표지를 명확히 표시한다. 파일럿 가정상 검색 결과 광고 비중은 최대 30%로 제한한다. 동일 광고주 상단 독점, 대형 광고주 편중, 과도한 반복 노출을 제한하고, 예산 페이싱과 카테고리별 최소 다양성을 적용한다. 최상단 AD·디스플레이·큐레이션과의 성과 및 예산 이동을 함께 모니터링한다.
-1. ○ Given 검색 결과가 생성되었을 때, When 광고와 오가닉 결과를 조합하면, Then 광고에는 광고 표지가 표시되고 오가닉 결과와 구분된다.
-2. ○ Given 광고 밀도가 사전 설정된 상한에 도달했을 때, When 추가 후보가 존재하면, Then 초과 후보는 노출되지 않고 오가닉 결과가 우선 배치된다.
+          <t>입찰 상단은 검색 결과 최상단과 일반 노출(입찰 미참여 제휴 쿠폰) 결과 사이의 혼합 영역에 배치하고 광고 표지를 명확히 표시한다. 파일럿 가정상 검색 결과 내 입찰 상단 비중은 최대 30%로 제한한다. 동일 광고주 상단 독점, 대형 광고주 편중, 과도한 반복 노출을 제한하고, 예산 페이싱과 카테고리별 최소 다양성을 적용한다. 최상단 AD·디스플레이·큐레이션과의 성과 및 예산 이동을 함께 모니터링한다.
+1. ○ Given 검색 결과가 생성되었을 때, When 입찰 상단과 일반 노출 결과를 조합하면, Then 입찰 상단에는 광고 표지가 표시되고 일반 노출 결과와 구분된다.
+2. ○ Given 입찰 상단 비중이 사전 설정된 상한에 도달했을 때, When 추가 후보가 존재하면, Then 초과 후보는 노출되지 않고 일반 노출 결과가 우선 배치된다.
 3. ○ Given 한 광고주가 상단 슬롯을 독점하려 할 때, When 다양성 정책을 평가하면, Then 광고주별 상단 노출 캡과 동일 쿠폰 반복 제한이 적용된다.
 4. ○ Given 신규 광고주가 최소 관련성 기준을 충족할 때, When 탐색 로직이 실행되면, Then 기존 고성과 광고주 외에도 제한된 탐색 기회가 배정된다.
-5. ○ Given 광고 지면 도입 후 디스플레이 매출 또는 오가닉 사용이 감소할 때, When 모니터링 임계값을 초과하면, Then 카테고리·광고주·지면별 노출을 조정하거나 파일럿을 축소한다.</t>
+5. ○ Given 입찰 상단 도입 후 디스플레이 매출 또는 일반 노출 쿠폰 사용이 감소할 때, When 모니터링 임계값을 초과하면, Then 카테고리·광고주·지면별 노출을 조정하거나 파일럿을 축소한다.</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr">
@@ -1189,27 +1189,27 @@
       <c r="B35" s="14" t="n"/>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>3.1 광고·오가닉 결과 배치</t>
+          <t>3.1 입찰 상단·일반 노출 결과 배치</t>
         </is>
       </c>
       <c r="D35" s="14" t="n"/>
       <c r="E35" s="16" t="inlineStr">
         <is>
-          <t>시스템은 검색광고를 최상단 광고 영역과 오가닉 결과 사이의 혼합 영역에 배치하고 광고임을 명확히 표시한다. 광고 비중은 파일럿 가정상 한 검색 결과의 최대 30%로 제한하며, 초과 후보보다 오가닉 결과를 우선한다. 최상단 AD와 디스플레이·큐레이션 상품의 성과 및 예산 이동은 함께 관찰한다.
-[기능의 근거] 검색광고는 수요 포착을 담당하되, 사용자의 검색 경험과 기존 오가닉·디스플레이 상품을 훼손하지 않아야 한다.
-[성공 기준] 한 검색 결과 내 광고 비중은 파일럿 가정상 30% 이하이고, 기존 디스플레이 매출 유지율은 90% 이상으로 측정된다.
+          <t>시스템은 입찰 상단을 검색 결과 최상단과 일반 노출(입찰 미참여 제휴 쿠폰) 결과 사이의 혼합 영역에 배치하고 광고임을 명확히 표시한다. 입찰 상단 비중은 파일럿 가정상 한 검색 결과의 최대 30%로 제한하며, 초과 후보보다 일반 노출 결과를 우선한다. 최상단 AD와 디스플레이·큐레이션 상품의 성과 및 예산 이동은 함께 관찰한다.
+[기능의 근거] 검색광고는 수요 포착을 담당하되, 사용자의 검색 경험과 일반 노출 쿠폰·기존 광고 구좌를 훼손하지 않아야 한다.
+[성공 기준] 한 검색 결과 내 입찰 상단 비중은 파일럿 가정상 30% 이하이고, 기존 디스플레이 매출 유지율은 90% 이상으로 측정된다.
 [개발 준비 슬롯]
-• 선행조건: - 경매가 노출 자격을 갖춘 광고 후보를 반환한다.
-• 오가닉 검색 결과가 존재한다.
+• 선행조건: - 경매가 노출 자격을 갖춘 입찰 상단 후보를 반환한다.
+• 일반 노출 검색 결과가 존재한다.
 • 트리거: - 사용자의 검색 결과를 구성한다.
-• 동작: - 시스템은 광고 후보를 최상단 또는 오가닉 결과 사이에 배치한다.
-• 시스템은 광고 밀도 상한을 적용한 뒤 남은 위치에 오가닉 결과를 배치한다.
-• 결과: - 사용자에게 광고 표지가 있는 검색 결과가 제공된다.
-• 예외: - 광고 후보가 없거나 광고 밀도 상한에 도달하면 오가닉 결과만 추가로 노출한다.
-• 표시: - 광고 결과는 오가닉 결과와 시각적으로 구분되는 광고 표지를 표시한다.
+• 동작: - 시스템은 입찰 상단 후보를 최상단 또는 일반 노출 결과 사이에 배치한다.
+• 시스템은 입찰 상단 비중 상한을 적용한 뒤 남은 위치에 일반 노출 결과를 배치한다.
+• 결과: - 사용자에게 광고 표지가 있는 입찰 상단과 일반 노출 결과가 제공된다.
+• 예외: - 입찰 상단 후보가 없거나 입찰 상단 비중 상한에 도달하면 일반 노출 결과만 추가로 노출한다.
+• 표시: - 입찰 상단 결과는 일반 노출 결과와 시각적으로 구분되는 광고 표지를 표시한다.
 • 권한 &amp; 접근: - 모든 사용자는 동일한 광고 표지 원칙이 적용된 검색 결과를 조회한다.
-• 비즈니스 규칙: - 검색 결과의 광고 비중은 파일럿 가정상 최대 30%로 제한한다.
-• 데이터: - 노출 레코드는 검색 요청, 광고 또는 오가닉 구분, 배치 위치, 광고 표지 여부를 가진다.</t>
+• 비즈니스 규칙: - 검색 결과의 입찰 상단 비중은 파일럿 가정상 최대 30%로 제한한다.
+• 데이터: - 노출 레코드는 검색 요청, 입찰 상단 또는 일반 노출 구분, 배치 위치, 광고 표지 여부를 가진다.</t>
         </is>
       </c>
       <c r="F35" s="17" t="inlineStr">
@@ -1246,7 +1246,7 @@
         <is>
           <t>시스템은 동일 광고주가 상단 슬롯을 반복 점유하거나 동일 쿠폰이 과도하게 노출되는 것을 제한한다. 관련성 최소 기준, 신규 광고주 콜드스타트 탐색 노출, 광고주별 다양성 캡, 예산 페이싱, 롱테일 키워드 분산을 경매와 노출 배치에 적용한다. 이 기능은 성과가 높은 대형 광고주의 입찰 기회를 일률적으로 배제하는 기능이 아니라 공정한 탐색과 사용자 선택권을 보장하는 범위로 제한한다.
 [기능의 근거] 예상 전환율이 높은 대형 광고주가 상단을 독식하면 신규·롱테일 광고주의 진입과 검색 결과의 다양성이 저해될 수 있다.
-[성공 기준] 오가닉 쿠폰 잠식률은 파일럿 가정상 10% 이하로 측정하고, 광고주별 상단 점유 분포를 모니터링한다.
+[성공 기준] 일반 노출 쿠폰 잠식률은 파일럿 가정상 10% 이하로 측정하고, 광고주별 상단 점유 분포를 모니터링한다.
 [개발 준비 슬롯]
 • 선행조건: - 경매 후보와 광고주의 최근 노출·예산 데이터가 존재한다.
 • 트리거: - 상단 및 혼합 영역의 광고 슬롯을 배정한다.
@@ -1378,7 +1378,7 @@
       <c r="D39" s="8" t="n"/>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>광고주와 내부 운영자에게 노출, 클릭, 쿠폰 발급, 쿠폰 사용, 토스페이 결제 확정, 거래액, 비용, CPC, CTR, CVR, ROAS, 환불, 오가닉 잠식률을 제공한다. 검색→쿠폰→토스페이 결제 경로를 이벤트로 연결하고 사용자 홀드아웃 A/B 및 캠페인별 증분 효과를 분석한다. 개인정보 보호를 위해 개인 식별 정보가 아닌 권한별 집계 결과를 제공한다.
+          <t>광고주와 내부 운영자에게 노출, 클릭, 쿠폰 발급, 쿠폰 사용, 토스페이 결제 확정, 거래액, 비용, CPC, CTR, CVR, ROAS, 환불, 일반 노출 쿠폰 잠식률을 제공한다. 검색→쿠폰→토스페이 결제 경로를 이벤트로 연결하고 사용자 홀드아웃 A/B 및 캠페인별 증분 효과를 분석한다. 개인정보 보호를 위해 개인 식별 정보가 아닌 권한별 집계 결과를 제공한다.
 1. ○ Given 광고 클릭이 발생했을 때, When 쿠폰 발급과 토스페이 결제가 이어지면, Then 클릭 ID·쿠폰 ID·전환 ID를 연결한 이벤트 경로가 생성된다.
 2. ○ Given 토스페이 결제가 확정되었을 때, When 리포트 집계를 실행하면, Then 결제 건수와 거래액이 확정 결제 기준으로 반영된다.
 3. ○ Given 결제가 취소 또는 환불되었을 때, When 후속 이벤트가 반영되면, Then 전환 수·거래액·ROAS·정산 금액이 정책에 따라 갱신된다.
@@ -1414,7 +1414,7 @@
       <c r="D40" s="14" t="n"/>
       <c r="E40" s="16" t="inlineStr">
         <is>
-          <t>광고주와 내부 운영자는 노출, 클릭, 쿠폰 발급·사용, 토스페이 결제 확정, 거래액, 비용, CPC, CTR, CVR, ROAS, 환불, 오가닉 잠식률을 권한별 집계로 조회한다. 일반 지표와 결제·정산 확정 지표의 신선도는 파일럿 가정으로 관리하며 실제 SLA는 기술 검증 후 확정한다. 원시 개인정보는 리포트에 제공하지 않는다.
+          <t>광고주와 내부 운영자는 노출, 클릭, 쿠폰 발급·사용, 토스페이 결제 확정, 거래액, 비용, CPC, CTR, CVR, ROAS, 환불, 일반 노출 쿠폰 잠식률을 권한별 집계로 조회한다. 일반 지표와 결제·정산 확정 지표의 신선도는 파일럿 가정으로 관리하며 실제 SLA는 기술 검증 후 확정한다. 원시 개인정보는 리포트에 제공하지 않는다.
 [기능의 근거] 광고주는 검색광고 집행 성과와 비용을 검증해야 하며, 토스는 광고 매출·결제 활성화·잠식 리스크를 함께 판단해야 한다.
 [성공 기준] 광고주 재집행과 캠페인 유지 비중을 측정하며, 파일럿 가정상 캠페인 유지 광고주 비중 50% 이상을 목표로 한다.
 [개발 준비 슬롯]
@@ -1516,9 +1516,9 @@
       <c r="D42" s="8" t="n"/>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>핵심 데이터 모델은 캠페인, 광고주, 쿠폰, 키워드·카테고리 입찰, 경매 후보, 노출, 클릭, 쿠폰 발급, 전환, 환불, 정산 원장, 실험군을 포함한다. 캠페인 상태는 초안→심사→집행중→소진/중단으로 관리한다. 전환 상태는 클릭→쿠폰 발급→토스페이 결제 확정→환불 차감으로 관리한다. API는 검색 경매 요청·응답, 클릭 수집, 전환 수집, 환불 수집, 리포트 조회를 제공하고 모든 이벤트 수집 API는 멱등키를 지원한다. 경매는 실시간 응답이 필요하며, 무효 클릭 탐지·장애 시 안전한 오가닉 폴백·역할기반 접근제어·감사 로그를 기본으로 한다.
+          <t>핵심 데이터 모델은 캠페인, 광고주, 쿠폰, 키워드·카테고리 입찰, 경매 후보, 노출, 클릭, 쿠폰 발급, 전환, 환불, 정산 원장, 실험군을 포함한다. 캠페인 상태는 초안→심사→집행중→소진/중단으로 관리한다. 전환 상태는 클릭→쿠폰 발급→토스페이 결제 확정→환불 차감으로 관리한다. API는 검색 경매 요청·응답, 클릭 수집, 전환 수집, 환불 수집, 리포트 조회를 제공하고 모든 이벤트 수집 API는 멱등키를 지원한다. 경매는 실시간 응답이 필요하며, 무효 클릭 탐지·장애 시 안전한 일반 노출 결과 폴백·역할기반 접근제어·감사 로그를 기본으로 한다.
 1. ○ Given 검색 경매 요청이 들어왔을 때, When 시스템이 정상 상태이면, Then 파일럿 가정상 300밀리초 이내에 후보와 순위, 광고 표지, 추적 정보를 응답한다. 실제 목표는 부하 테스트 후 확정한다.
-2. ○ Given 경매 서버 또는 광고 데이터 저장소가 장애인 상태일 때, When 제한시간을 초과하면, Then 오가닉 검색 결과를 반환하고 광고 과금을 발생시키지 않는다.
+2. ○ Given 경매 서버 또는 광고 데이터 저장소가 장애인 상태일 때, When 제한시간을 초과하면, Then 일반 노출 검색 결과를 반환하고 광고 과금을 발생시키지 않는다.
 3. ○ Given 클릭·전환·환불 이벤트가 재전송될 때, When 동일 멱등키를 검증하면, Then 중복 원장과 중복 전환이 생성되지 않는다.
 4. ○ Given 운영자 또는 광고주가 데이터에 접근할 때, When 역할과 캠페인 소유권을 확인하면, Then 허용된 범위만 조회·수정할 수 있고 모든 변경은 감사 로그에 남는다.
 5. ○ Given 비정상적으로 짧은 체류, 반복 IP·기기 패턴, 자동화 시그널이 탐지될 때, When 무효 클릭 판정을 실행하면, Then 과금에서 제외하고 탐지 결과를 리포트한다.
@@ -1549,18 +1549,18 @@
       <c r="D43" s="14" t="n"/>
       <c r="E43" s="16" t="inlineStr">
         <is>
-          <t>시스템은 검색 경매 요청·응답, 클릭 수집, 전환 수집, 환불 수집, 리포트 조회 API를 제공하고 모든 이벤트 수집 요청에 멱등키를 적용한다. 캠페인은 초안·심사·집행중·소진·중단 상태로, 전환은 클릭·쿠폰 발급·토스페이 결제 확정·환불 차감 상태로 관리한다. 경매 또는 광고 데이터 저장소에 장애가 발생하면 광고 과금 없이 오가닉 검색 결과로 안전하게 전환한다.
+          <t>시스템은 검색 경매 요청·응답, 클릭 수집, 전환 수집, 환불 수집, 리포트 조회 API를 제공하고 모든 이벤트 수집 요청에 멱등키를 적용한다. 캠페인은 초안·심사·집행중·소진·중단 상태로, 전환은 클릭·쿠폰 발급·토스페이 결제 확정·환불 차감 상태로 관리한다. 경매 또는 광고 데이터 저장소에 장애가 발생하면 광고 과금 없이 일반 노출 검색 결과로 안전하게 전환한다.
 [기능의 근거] 실시간 검색광고, 정확한 과금·측정, 안전한 장애 대응을 위해 공통 이벤트 인터페이스와 상태·데이터 통제가 필요하다.
 [성공 기준] 검색 경매 응답 시간과 무효 클릭률을 측정하며, 응답 시간 목표는 파일럿 가정상 300밀리초 이내로 두고 부하 테스트 후 확정한다.
 [개발 준비 슬롯]
 • 선행조건: - API 호출자는 역할과 캠페인 소유권에 따라 인증된다.
 • 트리거: - 검색 경매, 클릭·전환·환불 이벤트 수집, 리포트 조회 API가 호출된다.
 • 동작: - 시스템은 멱등키를 검증하고 이벤트를 상태 전이에 따라 저장한다.
-• 경매 장애 또는 제한시간 초과 시 오가닉 검색 결과를 반환한다.
+• 경매 장애 또는 제한시간 초과 시 일반 노출 검색 결과를 반환한다.
 • 결과: - 중복 원장과 중복 전환 없이 이벤트·상태·감사 로그가 저장된다.
-• 장애 시 광고 과금 없이 오가닉 결과가 제공된다.
-• 예외: - 경매 서버 또는 광고 데이터 저장소가 제한시간을 초과하면 광고를 노출하거나 과금하지 않는다.
-• 표시: - 사용자 화면은 장애 시 오가닉 검색 결과를 표시한다.
+• 장애 시 입찰 상단 과금 없이 일반 노출 결과가 제공된다.
+• 예외: - 경매 서버 또는 광고 데이터 저장소가 제한시간을 초과하면 입찰 상단을 노출하거나 과금하지 않는다.
+• 표시: - 사용자 화면은 장애 시 일반 노출 검색 결과를 표시한다.
 • 권한 &amp; 접근: - 운영자와 광고주는 역할·캠페인 소유권에 따라 허용된 데이터만 조회·수정할 수 있다.
 • 비즈니스 규칙: - 모든 변경은 감사 로그에 남긴다.
 • 개인정보와 민감한 행동 신호에는 동의·목적 제한·최소 수집·접근 통제·보유 기간 정책을 적용한다.
@@ -1599,7 +1599,7 @@
       <c r="D44" s="8" t="n"/>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>1단계는 쇼핑·리테일 및 뷰티·라이프스타일 카테고리에서 CPC 키워드·카테고리 입찰, 최상단·혼합 노출, 사용자 홀드아웃 A/B를 검증한다. 2단계는 카테고리·키워드 확대, 자동입찰, 목표 CPA를 도입한다. 3단계는 제한된 광고주 대상으로 CPS 보장형 티어와 개인화 검색 추천을 검토한다. 정책은 입찰 자격, 경매 품질·적합도, 광고 노출 배분, 소재·쿠폰 심사, 과금·정산, 기여 윈도우, 개인정보 처리, 이의제기 절차를 포함한다.
+          <t>1단계는 쇼핑·리테일 및 뷰티·라이프스타일 카테고리에서 CPC 키워드·카테고리 입찰, 입찰 상단·일반 노출 혼합, 사용자 홀드아웃 A/B를 검증한다. 2단계는 카테고리·키워드 확대, 자동입찰, 목표 CPA를 도입한다. 3단계는 제한된 광고주 대상으로 CPS 보장형 티어와 개인화 검색 추천을 검토한다. 정책은 입찰 자격, 경매 품질·적합도, 광고 노출 배분, 소재·쿠폰 심사, 과금·정산, 기여 윈도우, 개인정보 처리, 이의제기 절차를 포함한다.
 1. ○ Given 1단계 파일럿이 시작될 때, When 대상 카테고리·광고주·실험군을 확정하면, Then 사전 등록된 분석 계획과 성공·축소 기준이 잠긴다.
 2. ○ Given 파일럿 종료 시점이 되었을 때, When KPI와 리스크 지표를 분석하면, Then 확대·반복 실험·축소 중 하나의 의사결정 문서가 생성된다.
 3. ○ Given 자동입찰을 도입할 때, When 광고주의 목표 CPA와 예산 한도를 등록하면, Then 입찰 상한·학습 기간·중단 조건을 적용한다.
@@ -1632,15 +1632,15 @@
       <c r="E45" s="16" t="inlineStr">
         <is>
           <t>토스 광고 운영자는 1개 업종 전체를 대상으로 검색광고 파일럿을 운영하고, 사용자 홀드아웃 A/B 결과와 건전성 지표를 근거로 확대·반복 실험·축소 또는 중단을 결정한다. 초기 파일럿은 쇼핑·리테일 또는 뷰티·라이프스타일 중 내부 검증을 마친 1개 업종에서 실행하며, 성공 시 카테고리·키워드와 대상 광고주를 단계적으로 넓힌다. 이 기능은 광고 과금을 결정하지 않으며, CPC·CPS 과금은 별도 과금·정산 기능의 기준을 따른다.
-[기능의 근거] 쿠폰 검색량과 토스페이 결제의 순증 효과, 오가닉·디스플레이 잠식 위험을 실제 사용자 환경에서 검증한 뒤에만 상품 범위를 확대해야 한다.
-[성공 기준] 파일럿 가정상 순증 결제 효과, 광고주 재집행, 오가닉 쿠폰 잠식률 10% 이하, 무효 클릭률 2% 이하를 함께 확인해 확대 여부를 결정한다.
+[기능의 근거] 쿠폰 검색량과 토스페이 결제의 순증 효과, 일반 노출 쿠폰·기존 광고 구좌 잠식 위험을 실제 사용자 환경에서 검증한 뒤에만 상품 범위를 확대해야 한다.
+[성공 기준] 파일럿 가정상 순증 결제 효과, 광고주 재집행, 일반 노출 쿠폰 잠식률 10% 이하, 무효 클릭률 2% 이하를 함께 확인해 확대 여부를 결정한다.
 [개발 준비 슬롯]
 • 선행조건: - 내부 검증을 마친 1개 업종과 대상 광고주·사용자 실험군을 사전 등록한다.
 • 파일럿의 핵심 지표, 확대 게이트, 축소·중단 기준을 분석 계획에 기록한다.
 • 트리거: - 토스 광고 운영자가 1개 업종 전체 파일럿의 시작을 승인한다.
 • 파일럿 기간 종료 또는 축소·중단 임계값 초과가 발생한다.
-• 동작: - 시스템은 대상 업종의 광고 노출군과 홀드아웃 그룹을 분리해 운영한다.
-• 시스템은 순증 결제 효과, 광고주 재집행, 잠식률, 무효 클릭률, 광고 밀도를 집계한다.
+• 동작: - 시스템은 대상 업종의 입찰 상단 노출군과 홀드아웃 그룹을 분리해 운영한다.
+• 시스템은 순증 결제 효과, 광고주 재집행, 일반 노출 쿠폰 잠식률, 무효 클릭률, 입찰 상단 비중을 집계한다.
 • 운영자는 집계 결과에 따라 단계적 확대, 반복 실험, 노출 축소 또는 중단을 결정한다.
 • 결과: - 파일럿 결과와 확대·반복 실험·축소 또는 중단 결정이 기록된다.
 • 확대가 승인되면 다음 카테고리·키워드·광고주 범위가 단계적으로 활성화된다.
@@ -1653,7 +1653,7 @@
 • 토스 광고 운영자만 파일럿 범위와 광고 노출 상태를 변경할 수 있다.
 • 비즈니스 규칙: - 사용자 홀드아웃 A/B는 광고가 없어도 발생했을 전환을 제외한 순증 효과를 검증하는 의사결정 지표이며 CPC 또는 CPS 과금 기준이 아니다.
 • 1개 업종 전체 파일럿이 성공하면 카테고리·키워드·광고주 범위를 단계적으로 확대한다.
-• 오가닉 쿠폰 잠식률이 파일럿 가정상 15%를 초과하거나 무효 클릭률이 파일럿 가정상 5%를 초과하면 광고 노출을 축소한다.
+• 일반 노출 쿠폰 잠식률이 파일럿 가정상 15%를 초과하거나 무효 클릭률이 파일럿 가정상 5%를 초과하면 입찰 상단 노출을 축소한다.
 • 파일럿 확대의 순증 효과 통계 기준은 사전 검정력 분석 후 확정한다.
 • 데이터: - 파일럿 데이터는 업종, 카테고리, 키워드, 캠페인, 광고주, 실험군, 노출·클릭·쿠폰·결제·환불 지표, 잠식률, 무효 클릭률, 결정 상태, 결정 사유를 가진다.</t>
         </is>
